--- a/artfynd/A 49866-2024 artfynd.xlsx
+++ b/artfynd/A 49866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105537800</v>
+        <v>105537787</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,14 +710,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bäckebo, trädid F71537, Vg</t>
+          <t>Bäckebo, trädid F71546, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446808.8520451891</v>
+        <v>446817</v>
       </c>
       <c r="R2" t="n">
-        <v>6426729.114044402</v>
+        <v>6426722</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +744,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>F71537</t>
+          <t>F71546</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -757,19 +752,9 @@
           <t>2014-05-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-05-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105537801</v>
+        <v>105537788</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,14 +820,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäckebo, trädid F71536, Vg</t>
+          <t>Bäckebo, trädid F71545, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446818.8755899534</v>
+        <v>446814</v>
       </c>
       <c r="R3" t="n">
-        <v>6426723.677061274</v>
+        <v>6426726</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +854,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>F71536</t>
+          <t>F71545</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -882,19 +862,9 @@
           <t>2014-05-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-05-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,6 +888,666 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>105537795</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bäckebo, trädid F71539, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>446793</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6426730</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>F71539</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-05-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-05-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>105537797</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bäckebo, trädid F71538, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>446811</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6426722</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>F71538</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-05-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-05-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>105537800</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bäckebo, trädid F71537, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>446809</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6426729</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>F71537</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-05-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-05-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>105537801</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bäckebo, trädid F71536, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>446819</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6426723</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>F71536</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2014-05-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2014-05-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>105537802</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Övre Starbäck mm, trädid F71535, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>446828</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6426694</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>F71535</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2014-05-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2014-05-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>105537804</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Övre Starbäck mm, trädid F71534, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>446832</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6426690</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>F71534</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-05-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-05-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>

--- a/artfynd/A 49866-2024 artfynd.xlsx
+++ b/artfynd/A 49866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105537787</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105537788</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105537795</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105537797</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105537800</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105537801</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105537802</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,8 +1592,23 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105537804</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>